--- a/src/main/resources/Financial_Report_Field_Values.xlsx
+++ b/src/main/resources/Financial_Report_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63C265E9-4F6B-4384-AFEB-0C6D3D02E5A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69F3EB47-5BD3-4488-BECB-253298976F8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{1006BF38-9284-4AEF-804D-89E3CD329F3F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{1006BF38-9284-4AEF-804D-89E3CD329F3F}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>

--- a/src/main/resources/Financial_Report_Field_Values.xlsx
+++ b/src/main/resources/Financial_Report_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69F3EB47-5BD3-4488-BECB-253298976F8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D3295DF-8B3D-4331-A07E-90911E3CA95C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{1006BF38-9284-4AEF-804D-89E3CD329F3F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{1006BF38-9284-4AEF-804D-89E3CD329F3F}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="30">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -125,6 +125,9 @@
   </si>
   <si>
     <t>SubmittedOn__c</t>
+  </si>
+  <si>
+    <t>None</t>
   </si>
 </sst>
 </file>
@@ -530,7 +533,7 @@
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -546,7 +549,10 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B2" s="3" t="s">
+      <c r="A2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" t="s">
         <v>3</v>
       </c>
       <c r="C2">
@@ -579,6 +585,9 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>29</v>
+      </c>
       <c r="B2" s="3" t="s">
         <v>4</v>
       </c>
@@ -612,6 +621,9 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>29</v>
+      </c>
       <c r="B2" s="3" t="s">
         <v>5</v>
       </c>
@@ -620,6 +632,9 @@
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>29</v>
+      </c>
       <c r="B3" s="3" t="s">
         <v>7</v>
       </c>
@@ -628,6 +643,9 @@
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>29</v>
+      </c>
       <c r="B4" s="3" t="s">
         <v>9</v>
       </c>
@@ -636,6 +654,9 @@
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>29</v>
+      </c>
       <c r="B5" s="3" t="s">
         <v>11</v>
       </c>
@@ -644,6 +665,9 @@
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>29</v>
+      </c>
       <c r="B6" s="3" t="s">
         <v>13</v>
       </c>
@@ -652,6 +676,9 @@
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>29</v>
+      </c>
       <c r="B7" s="3" t="s">
         <v>17</v>
       </c>
@@ -660,6 +687,9 @@
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>29</v>
+      </c>
       <c r="B8" s="3" t="s">
         <v>15</v>
       </c>
@@ -668,6 +698,9 @@
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>29</v>
+      </c>
       <c r="B9" s="3" t="s">
         <v>19</v>
       </c>
@@ -676,6 +709,9 @@
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>29</v>
+      </c>
       <c r="B10" s="3" t="s">
         <v>21</v>
       </c>
@@ -684,6 +720,9 @@
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>29</v>
+      </c>
       <c r="B11" s="3" t="s">
         <v>23</v>
       </c>
@@ -692,6 +731,9 @@
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>29</v>
+      </c>
       <c r="B12" s="3" t="s">
         <v>25</v>
       </c>
@@ -700,6 +742,9 @@
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>29</v>
+      </c>
       <c r="B13" s="3" t="s">
         <v>26</v>
       </c>
@@ -708,6 +753,9 @@
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>29</v>
+      </c>
       <c r="B14" s="3" t="s">
         <v>28</v>
       </c>

--- a/src/main/resources/Financial_Report_Field_Values.xlsx
+++ b/src/main/resources/Financial_Report_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D3295DF-8B3D-4331-A07E-90911E3CA95C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B4D4572-1B06-422A-8108-7B1E9D57E19B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{1006BF38-9284-4AEF-804D-89E3CD329F3F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{1006BF38-9284-4AEF-804D-89E3CD329F3F}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>

--- a/src/main/resources/Financial_Report_Field_Values.xlsx
+++ b/src/main/resources/Financial_Report_Field_Values.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GovGrants Automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B4D4572-1B06-422A-8108-7B1E9D57E19B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35C42AF4-F3B0-4530-B47E-98E4A34E147A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{1006BF38-9284-4AEF-804D-89E3CD329F3F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{1006BF38-9284-4AEF-804D-89E3CD329F3F}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
     <sheet name="Submit Details" sheetId="2" r:id="rId2"/>
-    <sheet name="FederalFinancialReport_425" sheetId="3" r:id="rId3"/>
+    <sheet name="Final Financial report" sheetId="4" r:id="rId3"/>
+    <sheet name="FederalFinancialReport_425" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="33">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -128,6 +129,15 @@
   </si>
   <si>
     <t>None</t>
+  </si>
+  <si>
+    <t>Overview</t>
+  </si>
+  <si>
+    <t>Checked</t>
+  </si>
+  <si>
+    <t>IsFinalReport__c</t>
   </si>
 </sst>
 </file>
@@ -531,13 +541,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2476772-B920-4000-B039-6DADD34B954A}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -548,7 +558,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>29</v>
       </c>
@@ -567,13 +577,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3AF16F5-0C5E-4E87-9FD0-A70AFBBD7A87}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="18.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -584,7 +594,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>29</v>
       </c>
@@ -601,15 +611,52 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E843A54-CD6C-46A6-BCC9-FF9981E4EC5A}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="8.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.6328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35B0AEB4-FD56-466A-86EE-E835AAA9A36D}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -620,7 +667,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>29</v>
       </c>
@@ -631,7 +678,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>29</v>
       </c>
@@ -642,7 +689,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>29</v>
       </c>
@@ -653,7 +700,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>29</v>
       </c>
@@ -664,7 +711,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>29</v>
       </c>
@@ -675,7 +722,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>29</v>
       </c>
@@ -686,7 +733,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>29</v>
       </c>
@@ -697,7 +744,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>29</v>
       </c>
@@ -708,7 +755,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -719,7 +766,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>29</v>
       </c>
@@ -730,7 +777,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>29</v>
       </c>
@@ -741,7 +788,7 @@
         <v>8905890590</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>29</v>
       </c>
@@ -752,7 +799,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>29</v>
       </c>
